--- a/build/html/_static/techparas.xlsx
+++ b/build/html/_static/techparas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00 文档管理\01产品手册\01. 工业协作机器人手册\AGV\V01-kargoTest\source\_static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\001---jaka\V01-kargo\source\_static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6BDDD3-3BBA-4CF3-9F5F-8D63411ED573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BBDC6B-BF9F-4FDE-8F0E-C3F92BA50D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -54,15 +54,9 @@
     <t>6060-T6/Q235/ABS</t>
   </si>
   <si>
-    <t>底盘外形尺寸（长度*宽度*高度）</t>
-  </si>
-  <si>
     <t>841*641*313mm</t>
   </si>
   <si>
-    <t>升降柱外形尺寸（长度*宽度*高度）</t>
-  </si>
-  <si>
     <t>841*641*1750mm</t>
   </si>
   <si>
@@ -117,9 +111,6 @@
     <t>控制方式</t>
   </si>
   <si>
-    <t>JAKA Coboπ</t>
-  </si>
-  <si>
     <t>平均功率</t>
   </si>
   <si>
@@ -328,12 +319,6 @@
   </si>
   <si>
     <t>电池重量（单个）</t>
-  </si>
-  <si>
-    <t>9±2 kg</t>
-  </si>
-  <si>
-    <t>电池尺寸（长度*宽度*高度）</t>
   </si>
   <si>
     <t>345*120*155mm</t>
@@ -449,12 +434,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>USB*3
-RJ45*2
-HDMI*1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>千兆网口*5</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -476,6 +455,31 @@
   </si>
   <si>
     <t>1.5m</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>9±2kg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB*3
+RJ45*2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>JAKA Coboπ软件；SDK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>升降柱外形尺寸（长度×宽度×高度）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>底盘外形尺寸（长度×宽度×高度）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>电池尺寸（长度×宽度×高度）</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -728,6 +732,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -737,11 +753,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -752,12 +774,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -769,18 +785,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1063,789 +1067,732 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C80"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.625" customWidth="1"/>
-    <col min="3" max="3" width="22.375" customWidth="1"/>
+    <col min="1" max="1" width="28.58203125" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="24"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+      <c r="C1" s="10"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2" s="12"/>
+      <c r="C2" s="13"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="11"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C3" s="8"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="11"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C4" s="8"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="11"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C5" s="8"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="C6" s="8"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="11"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="C7" s="8"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="11"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="C8" s="8"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="11"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="C9" s="8"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="11"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="11"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="C11" s="8"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="11"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+      <c r="C12" s="8"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="11"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+      <c r="C13" s="8"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="11"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+      <c r="C14" s="8"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="11"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+      <c r="C15" s="8"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B16" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" s="8"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="11"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="B17" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="C17" s="8"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="11"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="B18" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="C18" s="8"/>
+    </row>
+    <row r="19" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="11"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+      <c r="B19" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" s="15"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="8"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="12"/>
+      <c r="C21" s="13"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="8"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="8"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="8"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="16">
+        <v>7</v>
+      </c>
+      <c r="C25" s="17"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C34" s="8"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="8"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="8"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="8"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="8"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="8"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="8"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="8"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="8"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="8"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" s="12"/>
+      <c r="C45" s="13"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="8"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" s="8"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C48" s="8"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C49" s="8"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" s="8"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="8"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" s="8"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C53" s="8"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" s="8"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C55" s="8"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C56" s="8"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C57" s="8"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C58" s="8"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B59" s="12"/>
+      <c r="C59" s="13"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C61" s="8"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C63" s="8"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C65" s="8"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C66" s="8"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C67" s="8"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C68" s="8"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C69" s="8"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C70" s="8"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C71" s="8"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C72" s="15"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="19"/>
+      <c r="B73" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C73" s="22"/>
+    </row>
+    <row r="74" spans="1:3" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="19"/>
+      <c r="B74" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="C74" s="22"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="19"/>
+      <c r="B75" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="11"/>
-    </row>
-    <row r="19" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="C19" s="16"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="11"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="9"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="11"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="11"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="11"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="21">
-        <v>7</v>
-      </c>
-      <c r="C25" s="22"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="C34" s="11"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C35" s="11"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="9"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="11"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="11"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="11"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" s="11"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C41" s="11"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C42" s="11"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C43" s="11"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" s="11"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="9"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" s="11"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C47" s="11"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C48" s="11"/>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C49" s="11"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="C50" s="11"/>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C51" s="11"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C52" s="11"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C53" s="11"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C54" s="11"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C55" s="11"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="C56" s="11"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C57" s="11"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="C58" s="11"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B59" s="8"/>
-      <c r="C59" s="9"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C61" s="11"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C63" s="11"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B64" s="8"/>
-      <c r="C64" s="9"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C65" s="11"/>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B66" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C66" s="11"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B67" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C67" s="11"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B68" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="C68" s="11"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B69" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="C69" s="11"/>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B70" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C70" s="11"/>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" s="2" t="s">
+      <c r="C75" s="22"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="20"/>
+      <c r="B76" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="C76" s="24"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B77" s="12"/>
+      <c r="C77" s="13"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C71" s="11"/>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" s="12" t="s">
+      <c r="B78" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B72" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="C72" s="16"/>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" s="13"/>
-      <c r="B73" s="17" t="s">
+      <c r="C78" s="8"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C73" s="18"/>
-    </row>
-    <row r="74" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="13"/>
-      <c r="B74" s="17" t="s">
+      <c r="B79" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C74" s="18"/>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" s="13"/>
-      <c r="B75" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C75" s="18"/>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" s="14"/>
-      <c r="B76" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="C76" s="20"/>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" s="7" t="s">
+      <c r="C79" s="8"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B77" s="8"/>
-      <c r="C77" s="9"/>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A78" s="2" t="s">
+      <c r="B80" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B78" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="C78" s="11"/>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B79" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="C79" s="11"/>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B80" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="C80" s="11"/>
+      <c r="C80" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B58:C58"/>
     <mergeCell ref="A77:C77"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
@@ -1860,6 +1807,63 @@
     <mergeCell ref="B74:C74"/>
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
